--- a/data/Terre di Pedemonte/investment_decision/Tegna_MFH_until_2004_investment_decision.xlsx
+++ b/data/Terre di Pedemonte/investment_decision/Tegna_MFH_until_2004_investment_decision.xlsx
@@ -461,22 +461,22 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>scen_cp_dr_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_dr_candidate_unit</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>scen_cp_cu_invested_available_unit</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>scen_cp_cu_candidate_unit</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_dr_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_dr_candidate_unit</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -532,7 +532,7 @@
         <v>47849</v>
       </c>
       <c r="B3" t="n">
-        <v>23.53835774367901</v>
+        <v>20.35671675387281</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -546,19 +546,19 @@
         <v>19590.93706844728</v>
       </c>
       <c r="F3" t="n">
-        <v>25.13408515667899</v>
+        <v>20.35671675387281</v>
       </c>
       <c r="G3" t="n">
         <v>19590.93706844728</v>
       </c>
       <c r="H3" t="n">
-        <v>23.53835774367901</v>
+        <v>20.35671675387281</v>
       </c>
       <c r="I3" t="n">
         <v>19590.93706844728</v>
       </c>
       <c r="J3" t="n">
-        <v>25.13408515667899</v>
+        <v>20.35671675387281</v>
       </c>
       <c r="K3" t="n">
         <v>19590.93706844728</v>
@@ -569,7 +569,7 @@
         <v>49675</v>
       </c>
       <c r="B4" t="n">
-        <v>64.75107912</v>
+        <v>70.78412446663532</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -583,19 +583,19 @@
         <v>19590.93706844728</v>
       </c>
       <c r="F4" t="n">
-        <v>82.42647506668909</v>
+        <v>70.21572899580775</v>
       </c>
       <c r="G4" t="n">
         <v>19590.93706844728</v>
       </c>
       <c r="H4" t="n">
-        <v>64.75107912</v>
+        <v>63.9854479581423</v>
       </c>
       <c r="I4" t="n">
         <v>19590.93706844728</v>
       </c>
       <c r="J4" t="n">
-        <v>82.42647506668909</v>
+        <v>64.19425366434501</v>
       </c>
       <c r="K4" t="n">
         <v>19590.93706844728</v>
@@ -606,7 +606,7 @@
         <v>51502</v>
       </c>
       <c r="B5" t="n">
-        <v>64.75107912</v>
+        <v>70.78412446663532</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -620,19 +620,19 @@
         <v>19590.93706844728</v>
       </c>
       <c r="F5" t="n">
-        <v>82.42647506668909</v>
+        <v>70.21572899580775</v>
       </c>
       <c r="G5" t="n">
         <v>19590.93706844728</v>
       </c>
       <c r="H5" t="n">
-        <v>64.75107912</v>
+        <v>63.9854479581423</v>
       </c>
       <c r="I5" t="n">
         <v>19590.93706844728</v>
       </c>
       <c r="J5" t="n">
-        <v>82.42647506668909</v>
+        <v>64.19425366434501</v>
       </c>
       <c r="K5" t="n">
         <v>19590.93706844728</v>
@@ -643,7 +643,7 @@
         <v>53328</v>
       </c>
       <c r="B6" t="n">
-        <v>64.75107912</v>
+        <v>70.78412446663532</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -657,19 +657,19 @@
         <v>19590.93706844728</v>
       </c>
       <c r="F6" t="n">
-        <v>82.42647506668909</v>
+        <v>70.21572899580775</v>
       </c>
       <c r="G6" t="n">
         <v>19590.93706844728</v>
       </c>
       <c r="H6" t="n">
-        <v>64.75107912</v>
+        <v>63.9854479581423</v>
       </c>
       <c r="I6" t="n">
         <v>19590.93706844728</v>
       </c>
       <c r="J6" t="n">
-        <v>82.42647506668909</v>
+        <v>64.19425366434501</v>
       </c>
       <c r="K6" t="n">
         <v>19590.93706844728</v>
@@ -684,32 +684,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Tegna_b_MFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Tegna_b_MFH_until_2004</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E7" t="n">
-        <v>29.38640560267093</v>
+        <v>43.72236867977528</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>16.73436751963556</v>
+        <v>43.72236867977528</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>29.38640560267093</v>
+        <v>24.89811772862284</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>16.73436751963556</v>
+        <v>24.89811772862284</v>
       </c>
     </row>
     <row r="8">
@@ -721,32 +721,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Tegna_b_MFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Tegna_b_MFH_until_2004</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E8" t="n">
-        <v>29.38640560267093</v>
+        <v>43.72236867977528</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>20.37048036428277</v>
+        <v>43.72236867977528</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>29.38640560267093</v>
+        <v>30.3080841091482</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>20.37048036428277</v>
+        <v>30.3080841091482</v>
       </c>
     </row>
     <row r="9">
@@ -758,32 +758,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Tegna_b_MFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Tegna_b_MFH_until_2004</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E9" t="n">
-        <v>29.38640560267093</v>
+        <v>43.72236867977528</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>21.85994184112424</v>
+        <v>43.72236867977528</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>29.38640560267093</v>
+        <v>32.52416948907865</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>21.85994184112424</v>
+        <v>32.52416948907865</v>
       </c>
     </row>
     <row r="10">
@@ -795,32 +795,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Tegna_b_MFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Tegna_b_MFH_until_2004</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E10" t="n">
-        <v>29.38640560267093</v>
+        <v>43.72236867977528</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>22.65612716278843</v>
+        <v>43.72236867977528</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>29.38640560267093</v>
+        <v>33.7087685394662</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>22.65612716278843</v>
+        <v>33.7087685394662</v>
       </c>
     </row>
     <row r="11">
@@ -832,32 +832,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Tegna_b_MFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Tegna_b_MFH_until_2004</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E11" t="n">
-        <v>29.38640560267093</v>
+        <v>43.72236867977528</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>23.15364032475919</v>
+        <v>43.72236867977528</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>29.38640560267093</v>
+        <v>34.4489901979037</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>23.15364032475919</v>
+        <v>34.4489901979037</v>
       </c>
     </row>
     <row r="12">
@@ -865,7 +865,7 @@
         <v>46023</v>
       </c>
       <c r="B12" t="n">
-        <v>0.006665552262352941</v>
+        <v>0.004026292260395426</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -879,19 +879,19 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.006665552262352941</v>
+        <v>0.004026292260395426</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.006665552262352941</v>
+        <v>0.004026292260395426</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0.006665552262352941</v>
+        <v>0.004026292260395426</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
@@ -902,7 +902,7 @@
         <v>47849</v>
       </c>
       <c r="B13" t="n">
-        <v>0.007300366763529412</v>
+        <v>0.00539592326</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -916,19 +916,19 @@
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0.007300366763529412</v>
+        <v>0.00539592326</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.007300366763529412</v>
+        <v>0.00539592326</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0.007300366763529412</v>
+        <v>0.00539592326</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -939,7 +939,7 @@
         <v>49675</v>
       </c>
       <c r="B14" t="n">
-        <v>0.007617774014117645</v>
+        <v>0.006665552262352942</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -953,19 +953,19 @@
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0.007617774014117645</v>
+        <v>0.006665552262352941</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.007617774014117645</v>
+        <v>0.006030737761176471</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0.007617774014117645</v>
+        <v>0.006030737761176471</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -976,7 +976,7 @@
         <v>51502</v>
       </c>
       <c r="B15" t="n">
-        <v>0.007617774014117645</v>
+        <v>0.006665552262352941</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -990,19 +990,19 @@
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0.007617774014117645</v>
+        <v>0.006665552262352942</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.007617774014117645</v>
+        <v>0.006030737761176471</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.007617774014117645</v>
+        <v>0.006030737761176471</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -1013,7 +1013,7 @@
         <v>53328</v>
       </c>
       <c r="B16" t="n">
-        <v>0.007617774014117645</v>
+        <v>0.006665552262352942</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1027,19 +1027,19 @@
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0.007617774014117645</v>
+        <v>0.006665552262352942</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.007617774014117645</v>
+        <v>0.006030737761176471</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.007617774014117645</v>
+        <v>0.006030737761176471</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -1124,7 +1124,7 @@
         <v>49675</v>
       </c>
       <c r="B19" t="n">
-        <v>0.4001362805594266</v>
+        <v>0.3832428000630117</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1138,19 +1138,19 @@
         <v>1.1331438846</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4001362805594266</v>
+        <v>0.3832428000630115</v>
       </c>
       <c r="G19" t="n">
         <v>1.1331438846</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4001362805594266</v>
+        <v>0.2820692389380116</v>
       </c>
       <c r="I19" t="n">
         <v>1.1331438846</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4001362805594266</v>
+        <v>0.2820692389380116</v>
       </c>
       <c r="K19" t="n">
         <v>1.1331438846</v>
@@ -1161,7 +1161,7 @@
         <v>51502</v>
       </c>
       <c r="B20" t="n">
-        <v>0.4001362805594266</v>
+        <v>0.3832428000630117</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1175,19 +1175,19 @@
         <v>1.1331438846</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4001362805594266</v>
+        <v>0.3832428000630115</v>
       </c>
       <c r="G20" t="n">
         <v>1.1331438846</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4001362805594266</v>
+        <v>0.2820692389380116</v>
       </c>
       <c r="I20" t="n">
         <v>1.1331438846</v>
       </c>
       <c r="J20" t="n">
-        <v>0.4001362805594266</v>
+        <v>0.2820692389380116</v>
       </c>
       <c r="K20" t="n">
         <v>1.1331438846</v>
@@ -1198,7 +1198,7 @@
         <v>53328</v>
       </c>
       <c r="B21" t="n">
-        <v>0.4001362805594266</v>
+        <v>0.3832428000630117</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1212,19 +1212,19 @@
         <v>1.1331438846</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4001362805594266</v>
+        <v>0.3832428000630115</v>
       </c>
       <c r="G21" t="n">
         <v>1.1331438846</v>
       </c>
       <c r="H21" t="n">
-        <v>0.4001362805594266</v>
+        <v>0.2820692389380116</v>
       </c>
       <c r="I21" t="n">
         <v>1.1331438846</v>
       </c>
       <c r="J21" t="n">
-        <v>0.4001362805594266</v>
+        <v>0.2820692389380116</v>
       </c>
       <c r="K21" t="n">
         <v>1.1331438846</v>
@@ -1494,7 +1494,7 @@
         <v>49675</v>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>0.033724520375</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1508,19 +1508,19 @@
         <v>1.1331438846</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>0.033724520375</v>
       </c>
       <c r="G29" t="n">
         <v>1.1331438846</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>0.1348980814999999</v>
       </c>
       <c r="I29" t="n">
         <v>1.1331438846</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>0.1348980814999999</v>
       </c>
       <c r="K29" t="n">
         <v>1.1331438846</v>
@@ -1531,7 +1531,7 @@
         <v>51502</v>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>0.033724520375</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1545,19 +1545,19 @@
         <v>1.1331438846</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>0.033724520375</v>
       </c>
       <c r="G30" t="n">
         <v>1.1331438846</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>0.1348980814999999</v>
       </c>
       <c r="I30" t="n">
         <v>1.1331438846</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.1348980814999999</v>
       </c>
       <c r="K30" t="n">
         <v>1.1331438846</v>
@@ -1568,7 +1568,7 @@
         <v>53328</v>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>0.033724520375</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1582,19 +1582,19 @@
         <v>1.1331438846</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>0.033724520375</v>
       </c>
       <c r="G31" t="n">
         <v>1.1331438846</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>0.1348980814999999</v>
       </c>
       <c r="I31" t="n">
         <v>1.1331438846</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>0.1348980814999999</v>
       </c>
       <c r="K31" t="n">
         <v>1.1331438846</v>
@@ -1992,13 +1992,13 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
+        <v>11.53959598494354</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
         <v>6.690945870182633</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" t="n">
-        <v>11.53959598494354</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -2029,13 +2029,13 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
+        <v>11.53959598494354</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
         <v>8.135107123830178</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" t="n">
-        <v>11.53959598494354</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -2066,13 +2066,13 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
+        <v>11.53959598494354</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
         <v>8.729853155642802</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" t="n">
-        <v>11.53959598494354</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -2103,13 +2103,13 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
+        <v>11.53959598494354</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
         <v>9.052254051979041</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" t="n">
-        <v>11.53959598494354</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -2140,13 +2140,13 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
+        <v>11.53959598494354</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
         <v>9.25714062299801</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" t="n">
-        <v>11.53959598494354</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -2362,13 +2362,13 @@
         <v>0</v>
       </c>
       <c r="G52" t="n">
+        <v>5.390198763604375</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="n">
         <v>1.691201479141251</v>
-      </c>
-      <c r="H52" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" t="n">
-        <v>5.390198763604375</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -2399,13 +2399,13 @@
         <v>0</v>
       </c>
       <c r="G53" t="n">
+        <v>5.390198763604375</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
         <v>2.224747042778638</v>
-      </c>
-      <c r="H53" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" t="n">
-        <v>5.390198763604375</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -2419,7 +2419,7 @@
         <v>49675</v>
       </c>
       <c r="B54" t="n">
-        <v>1.858546388127084</v>
+        <v>1.794049816811285</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2433,19 +2433,19 @@
         <v>5.390198763604375</v>
       </c>
       <c r="F54" t="n">
-        <v>1.833064755647154</v>
+        <v>1.789514563615505</v>
       </c>
       <c r="G54" t="n">
+        <v>5.390198763604375</v>
+      </c>
+      <c r="H54" t="n">
+        <v>1.802187697949361</v>
+      </c>
+      <c r="I54" t="n">
         <v>2.462521204213318</v>
       </c>
-      <c r="H54" t="n">
-        <v>1.797122160741155</v>
-      </c>
-      <c r="I54" t="n">
-        <v>5.390198763604375</v>
-      </c>
       <c r="J54" t="n">
-        <v>1.810005061384002</v>
+        <v>1.800377473584317</v>
       </c>
       <c r="K54" t="n">
         <v>2.462521204213318</v>
@@ -2456,7 +2456,7 @@
         <v>51502</v>
       </c>
       <c r="B55" t="n">
-        <v>1.858546388127084</v>
+        <v>1.794049816811285</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2470,19 +2470,19 @@
         <v>5.390198763604375</v>
       </c>
       <c r="F55" t="n">
-        <v>1.833064755647154</v>
+        <v>1.789514563615505</v>
       </c>
       <c r="G55" t="n">
+        <v>5.390198763604375</v>
+      </c>
+      <c r="H55" t="n">
+        <v>1.802187697949361</v>
+      </c>
+      <c r="I55" t="n">
         <v>2.59084275598636</v>
       </c>
-      <c r="H55" t="n">
-        <v>1.797122160741155</v>
-      </c>
-      <c r="I55" t="n">
-        <v>5.390198763604375</v>
-      </c>
       <c r="J55" t="n">
-        <v>1.810005061384002</v>
+        <v>1.800377473584317</v>
       </c>
       <c r="K55" t="n">
         <v>2.59084275598636</v>
@@ -2493,7 +2493,7 @@
         <v>53328</v>
       </c>
       <c r="B56" t="n">
-        <v>1.858546388127084</v>
+        <v>1.794049816811285</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2507,19 +2507,19 @@
         <v>5.390198763604375</v>
       </c>
       <c r="F56" t="n">
-        <v>1.833064755647154</v>
+        <v>1.789514563615505</v>
       </c>
       <c r="G56" t="n">
+        <v>5.390198763604375</v>
+      </c>
+      <c r="H56" t="n">
+        <v>1.802187697949361</v>
+      </c>
+      <c r="I56" t="n">
         <v>2.670056471603163</v>
       </c>
-      <c r="H56" t="n">
-        <v>1.797122160741155</v>
-      </c>
-      <c r="I56" t="n">
-        <v>5.390198763604375</v>
-      </c>
       <c r="J56" t="n">
-        <v>1.810005061384002</v>
+        <v>1.800377473584317</v>
       </c>
       <c r="K56" t="n">
         <v>2.670056471603163</v>
@@ -2547,13 +2547,13 @@
         <v>0</v>
       </c>
       <c r="G57" t="n">
+        <v>5.390198763604375</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="n">
         <v>1.691201479141251</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" t="n">
-        <v>5.390198763604375</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -2584,13 +2584,13 @@
         <v>0</v>
       </c>
       <c r="G58" t="n">
+        <v>5.390198763604375</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
         <v>2.224747042778638</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" t="n">
-        <v>5.390198763604375</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -2621,13 +2621,13 @@
         <v>0</v>
       </c>
       <c r="G59" t="n">
+        <v>5.390198763604375</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="n">
         <v>2.462521204213318</v>
-      </c>
-      <c r="H59" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" t="n">
-        <v>5.390198763604375</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -2658,13 +2658,13 @@
         <v>0</v>
       </c>
       <c r="G60" t="n">
+        <v>5.390198763604375</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="n">
         <v>2.59084275598636</v>
-      </c>
-      <c r="H60" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" t="n">
-        <v>5.390198763604375</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -2695,13 +2695,13 @@
         <v>0</v>
       </c>
       <c r="G61" t="n">
+        <v>5.390198763604375</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" t="n">
         <v>2.670056471603163</v>
-      </c>
-      <c r="H61" t="n">
-        <v>0</v>
-      </c>
-      <c r="I61" t="n">
-        <v>5.390198763604375</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -2789,7 +2789,7 @@
         <v>49675</v>
       </c>
       <c r="B64" t="n">
-        <v>1.155257904014526</v>
+        <v>0.4217454263889653</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2803,19 +2803,19 @@
         <v>5.390198763604375</v>
       </c>
       <c r="F64" t="n">
-        <v>1.09788611799435</v>
+        <v>0.4296511673592212</v>
       </c>
       <c r="G64" t="n">
         <v>5.390198763604375</v>
       </c>
       <c r="H64" t="n">
-        <v>1.216682131400454</v>
+        <v>0.4682706376926443</v>
       </c>
       <c r="I64" t="n">
         <v>5.390198763604375</v>
       </c>
       <c r="J64" t="n">
-        <v>1.120945812257502</v>
+        <v>0.4662064365343828</v>
       </c>
       <c r="K64" t="n">
         <v>5.390198763604375</v>
@@ -2826,7 +2826,7 @@
         <v>51502</v>
       </c>
       <c r="B65" t="n">
-        <v>1.155257904014526</v>
+        <v>0.4217454263889653</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2840,19 +2840,19 @@
         <v>5.390198763604375</v>
       </c>
       <c r="F65" t="n">
-        <v>1.09788611799435</v>
+        <v>0.4296511673592212</v>
       </c>
       <c r="G65" t="n">
         <v>5.390198763604375</v>
       </c>
       <c r="H65" t="n">
-        <v>1.216682131400455</v>
+        <v>0.4682706376926443</v>
       </c>
       <c r="I65" t="n">
         <v>5.390198763604375</v>
       </c>
       <c r="J65" t="n">
-        <v>1.120945812257502</v>
+        <v>0.4662064365343828</v>
       </c>
       <c r="K65" t="n">
         <v>5.390198763604375</v>
@@ -2863,7 +2863,7 @@
         <v>53328</v>
       </c>
       <c r="B66" t="n">
-        <v>1.300242918188542</v>
+        <v>0.4217454263889653</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2877,19 +2877,19 @@
         <v>5.390198763604375</v>
       </c>
       <c r="F66" t="n">
-        <v>1.242871132168366</v>
+        <v>0.4296511673592213</v>
       </c>
       <c r="G66" t="n">
         <v>5.390198763604375</v>
       </c>
       <c r="H66" t="n">
-        <v>1.361667145574471</v>
+        <v>0.4682706376926443</v>
       </c>
       <c r="I66" t="n">
         <v>5.390198763604375</v>
       </c>
       <c r="J66" t="n">
-        <v>1.265930826431519</v>
+        <v>0.4662064365343828</v>
       </c>
       <c r="K66" t="n">
         <v>5.390198763604375</v>
@@ -3102,7 +3102,7 @@
         <v>0</v>
       </c>
       <c r="G72" t="n">
-        <v>0.1668214327466203</v>
+        <v>5.390198763604375</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>0.1668214327466203</v>
+        <v>5.390198763604375</v>
       </c>
     </row>
     <row r="73">
@@ -3139,7 +3139,7 @@
         <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>0.2583650571086323</v>
+        <v>5.390198763604375</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
@@ -3151,7 +3151,7 @@
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>0.2583650571086323</v>
+        <v>5.390198763604375</v>
       </c>
     </row>
     <row r="74">
@@ -3176,7 +3176,7 @@
         <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>0.3187166551670044</v>
+        <v>5.390198763604375</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -3188,7 +3188,7 @@
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>0.3187166551670044</v>
+        <v>5.390198763604375</v>
       </c>
     </row>
     <row r="75">
@@ -3213,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>0.3626635053965984</v>
+        <v>5.390198763604375</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -3225,7 +3225,7 @@
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>0.3626635053965984</v>
+        <v>5.390198763604375</v>
       </c>
     </row>
     <row r="76">
@@ -3250,7 +3250,7 @@
         <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>0.3966817660001058</v>
+        <v>5.390198763604375</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -3262,7 +3262,7 @@
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>0.3966817660001058</v>
+        <v>5.390198763604375</v>
       </c>
     </row>
     <row r="77">
@@ -3287,7 +3287,7 @@
         <v>0</v>
       </c>
       <c r="G77" t="n">
-        <v>0.1668214327466203</v>
+        <v>5.390198763604375</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
@@ -3299,7 +3299,7 @@
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>0.1668214327466203</v>
+        <v>5.390198763604375</v>
       </c>
     </row>
     <row r="78">
@@ -3324,7 +3324,7 @@
         <v>0</v>
       </c>
       <c r="G78" t="n">
-        <v>0.2583650571086323</v>
+        <v>5.390198763604375</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
@@ -3336,7 +3336,7 @@
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>0.2583650571086323</v>
+        <v>5.390198763604375</v>
       </c>
     </row>
     <row r="79">
@@ -3361,7 +3361,7 @@
         <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>0.3187166551670044</v>
+        <v>5.390198763604375</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>
@@ -3373,7 +3373,7 @@
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>0.3187166551670044</v>
+        <v>5.390198763604375</v>
       </c>
     </row>
     <row r="80">
@@ -3398,7 +3398,7 @@
         <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>0.3626635053965984</v>
+        <v>5.390198763604375</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -3410,7 +3410,7 @@
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>0.3626635053965984</v>
+        <v>5.390198763604375</v>
       </c>
     </row>
     <row r="81">
@@ -3435,7 +3435,7 @@
         <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>0.3966817660001058</v>
+        <v>5.390198763604375</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
@@ -3447,7 +3447,7 @@
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>0.3966817660001058</v>
+        <v>5.390198763604375</v>
       </c>
     </row>
     <row r="82">
@@ -3470,13 +3470,13 @@
         <v>0</v>
       </c>
       <c r="G82" t="n">
+        <v>1</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" t="n">
         <v>0.4293250562242569</v>
-      </c>
-      <c r="H82" t="n">
-        <v>0</v>
-      </c>
-      <c r="I82" t="n">
-        <v>1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -3505,13 +3505,13 @@
         <v>0</v>
       </c>
       <c r="G83" t="n">
+        <v>1</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" t="n">
         <v>0.5615523961267772</v>
-      </c>
-      <c r="H83" t="n">
-        <v>0</v>
-      </c>
-      <c r="I83" t="n">
-        <v>1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -3540,13 +3540,13 @@
         <v>0</v>
       </c>
       <c r="G84" t="n">
+        <v>1</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" t="n">
         <v>0.624556919057325</v>
-      </c>
-      <c r="H84" t="n">
-        <v>0</v>
-      </c>
-      <c r="I84" t="n">
-        <v>1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -3575,13 +3575,13 @@
         <v>0</v>
       </c>
       <c r="G85" t="n">
+        <v>1</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" t="n">
         <v>0.6622379613453093</v>
-      </c>
-      <c r="H85" t="n">
-        <v>0</v>
-      </c>
-      <c r="I85" t="n">
-        <v>1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -3610,13 +3610,13 @@
         <v>0</v>
       </c>
       <c r="G86" t="n">
+        <v>1</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" t="n">
         <v>0.6881588528152967</v>
-      </c>
-      <c r="H86" t="n">
-        <v>0</v>
-      </c>
-      <c r="I86" t="n">
-        <v>1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -3645,13 +3645,13 @@
         <v>0</v>
       </c>
       <c r="G87" t="n">
+        <v>1</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" t="n">
         <v>0.4293250562242569</v>
-      </c>
-      <c r="H87" t="n">
-        <v>0</v>
-      </c>
-      <c r="I87" t="n">
-        <v>1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -3680,13 +3680,13 @@
         <v>0</v>
       </c>
       <c r="G88" t="n">
+        <v>1</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" t="n">
         <v>0.5615523961267772</v>
-      </c>
-      <c r="H88" t="n">
-        <v>0</v>
-      </c>
-      <c r="I88" t="n">
-        <v>1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -3715,13 +3715,13 @@
         <v>0</v>
       </c>
       <c r="G89" t="n">
+        <v>1</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" t="n">
         <v>0.624556919057325</v>
-      </c>
-      <c r="H89" t="n">
-        <v>0</v>
-      </c>
-      <c r="I89" t="n">
-        <v>1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -3750,13 +3750,13 @@
         <v>0</v>
       </c>
       <c r="G90" t="n">
+        <v>1</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" t="n">
         <v>0.6622379613453093</v>
-      </c>
-      <c r="H90" t="n">
-        <v>0</v>
-      </c>
-      <c r="I90" t="n">
-        <v>1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="G91" t="n">
+        <v>1</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" t="n">
         <v>0.6881588528152967</v>
-      </c>
-      <c r="H91" t="n">
-        <v>0</v>
-      </c>
-      <c r="I91" t="n">
-        <v>1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -3820,13 +3820,13 @@
         <v>0</v>
       </c>
       <c r="G92" t="n">
+        <v>1</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" t="n">
         <v>0.4293250562242569</v>
-      </c>
-      <c r="H92" t="n">
-        <v>0</v>
-      </c>
-      <c r="I92" t="n">
-        <v>1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -3855,13 +3855,13 @@
         <v>0</v>
       </c>
       <c r="G93" t="n">
+        <v>1</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" t="n">
         <v>0.5615523961267772</v>
-      </c>
-      <c r="H93" t="n">
-        <v>0</v>
-      </c>
-      <c r="I93" t="n">
-        <v>1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="G94" t="n">
+        <v>1</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" t="n">
         <v>0.624556919057325</v>
-      </c>
-      <c r="H94" t="n">
-        <v>0</v>
-      </c>
-      <c r="I94" t="n">
-        <v>1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -3925,13 +3925,13 @@
         <v>0</v>
       </c>
       <c r="G95" t="n">
+        <v>1</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" t="n">
         <v>0.6622379613453093</v>
-      </c>
-      <c r="H95" t="n">
-        <v>0</v>
-      </c>
-      <c r="I95" t="n">
-        <v>1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -3960,13 +3960,13 @@
         <v>0</v>
       </c>
       <c r="G96" t="n">
+        <v>1</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" t="n">
         <v>0.6881588528152967</v>
-      </c>
-      <c r="H96" t="n">
-        <v>0</v>
-      </c>
-      <c r="I96" t="n">
-        <v>1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
